--- a/data/trans_orig/P37A$vacunaempresa-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P37A$vacunaempresa-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>8019</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485210</t>
+          <t>486045</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>493163</t>
+          <t>493168</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>462989</t>
+          <t>463487</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>951686</t>
+          <t>952620</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>960630</t>
+          <t>960485</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,89%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17148</t>
+          <t>17339</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15531</t>
+          <t>13998</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26741</t>
+          <t>26547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>718341</t>
+          <t>718150</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>730669</t>
+          <t>730834</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>609963</t>
+          <t>611496</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>622337</t>
+          <t>622326</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1334241</t>
+          <t>1334435</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1351374</t>
+          <t>1351310</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>22624</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11399</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29103</t>
+          <t>29908</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>615530</t>
+          <t>616044</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>631745</t>
+          <t>631620</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>677842</t>
+          <t>677915</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>687752</t>
+          <t>687762</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1299309</t>
+          <t>1298504</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1317013</t>
+          <t>1316970</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13266</t>
+          <t>13715</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>14068</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>505881</t>
+          <t>505432</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>516182</t>
+          <t>516180</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1020278</t>
+          <t>1020721</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1031811</t>
+          <t>1031898</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>852</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>921</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>7669</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12124</t>
+          <t>11329</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>379539</t>
+          <t>378639</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>385869</t>
+          <t>385858</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>395846</t>
+          <t>396317</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>403064</t>
+          <t>403065</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>778572</t>
+          <t>779367</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>336643</t>
+          <t>336885</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>631037</t>
+          <t>631017</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24270</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48014</t>
+          <t>48567</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28389</t>
+          <t>28172</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39283</t>
+          <t>39214</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>66045</t>
+          <t>68139</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3228529</t>
+          <t>3227976</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3252273</t>
+          <t>3251959</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3350808</t>
+          <t>3351025</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3367600</t>
+          <t>3368201</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6589696</t>
+          <t>6587602</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6616458</t>
+          <t>6616527</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15357</t>
+          <t>17245</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2997</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16750</t>
+          <t>15654</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>438789</t>
+          <t>436901</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452064</t>
+          <t>451833</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>424707</t>
+          <t>424604</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>867626</t>
+          <t>868722</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>881402</t>
+          <t>881379</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>17059</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18232</t>
+          <t>19020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12340</t>
+          <t>12457</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30834</t>
+          <t>29959</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>670814</t>
+          <t>670028</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>682349</t>
+          <t>682286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>592023</t>
+          <t>591235</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>605439</t>
+          <t>605410</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1266508</t>
+          <t>1267383</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1285002</t>
+          <t>1284885</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23811</t>
+          <t>23486</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,82 +4413,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>12646</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6721</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21183</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>26717</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>16997</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>38544</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>1,22%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>12646</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6125</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22280</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>26717</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>17516</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>38312</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>658052</t>
+          <t>658377</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>673566</t>
+          <t>673737</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,82 +4526,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>98,81%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>698204</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>689667</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>704129</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,22%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,02%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1365995</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1354168</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1375715</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>98,08%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>97,23%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>98,78%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>698204</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>688570</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>704725</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,87%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1293</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1365995</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1354400</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1375196</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>98,08%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>97,25%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21056</t>
+          <t>23476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13290</t>
+          <t>13508</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>9257</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30622</t>
+          <t>29002</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>593561</t>
+          <t>591141</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>609479</t>
+          <t>609337</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>602909</t>
+          <t>602691</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>615085</t>
+          <t>614265</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1200194</t>
+          <t>1201814</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1221571</t>
+          <t>1221559</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>14558</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15929</t>
+          <t>14064</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>416644</t>
+          <t>414871</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>428338</t>
+          <t>428334</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>442477</t>
+          <t>442466</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>861300</t>
+          <t>863165</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>875080</t>
+          <t>875103</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>349134</t>
+          <t>349151</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>658920</t>
+          <t>658280</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34617</t>
+          <t>34748</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64547</t>
+          <t>64513</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21545</t>
+          <t>20789</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43891</t>
+          <t>44556</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60565</t>
+          <t>61116</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>98393</t>
+          <t>100264</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3362232</t>
+          <t>3362266</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3392162</t>
+          <t>3392031</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3514418</t>
+          <t>3513753</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3536764</t>
+          <t>3537520</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6886695</t>
+          <t>6884824</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6924523</t>
+          <t>6923972</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>391060</t>
+          <t>391030</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>810120</t>
+          <t>809847</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11896</t>
+          <t>11957</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>841</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16526</t>
+          <t>16651</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>578600</t>
+          <t>578539</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>588456</t>
+          <t>588484</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>555464</t>
+          <t>555023</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562698</t>
+          <t>562703</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1137514</t>
+          <t>1137389</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1150159</t>
+          <t>1150120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>16079</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17863</t>
+          <t>17664</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>662967</t>
+          <t>662974</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>646055</t>
+          <t>645307</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657792</t>
+          <t>657700</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1312620</t>
+          <t>1312819</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1325899</t>
+          <t>1325523</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>11424</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12731</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>18294</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>634621</t>
+          <t>634624</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>645046</t>
+          <t>645043</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>636346</t>
+          <t>635837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>647252</t>
+          <t>647980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1276159</t>
+          <t>1276831</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1291149</t>
+          <t>1291172</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>11079</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>14732</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>466141</t>
+          <t>466839</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>488729</t>
+          <t>489794</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>959985</t>
+          <t>960035</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>972533</t>
+          <t>972442</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9042</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26472</t>
+          <t>25994</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11815</t>
+          <t>11466</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29907</t>
+          <t>28883</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23057</t>
+          <t>23846</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>47937</t>
+          <t>49113</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3367878</t>
+          <t>3368356</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3385308</t>
+          <t>3385464</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3514635</t>
+          <t>3515659</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3532727</t>
+          <t>3533076</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6890955</t>
+          <t>6889779</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6915835</t>
+          <t>6915046</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20961</t>
+          <t>15025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>12349</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21838</t>
+          <t>22666</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,22 +9735,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17864</t>
+          <t>17649</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>9178</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32596</t>
+          <t>31298</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>393527</t>
+          <t>402493</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>379026</t>
+          <t>392768</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398736</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>301796</t>
+          <t>350163</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>291362</t>
+          <t>339846</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308092</t>
+          <t>356873</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,27 +9848,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>695323</t>
+          <t>752656</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>680591</t>
+          <t>739007</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>704727</t>
+          <t>761127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8945</t>
+          <t>10233</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19328</t>
+          <t>20195</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>19538</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>11174</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30143</t>
+          <t>29263</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27554</t>
+          <t>29771</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>18881</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41836</t>
+          <t>42384</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>414602</t>
+          <t>466657</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>404219</t>
+          <t>456695</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420310</t>
+          <t>473054</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>493484</t>
+          <t>482195</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>481950</t>
+          <t>472470</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502612</t>
+          <t>490559</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>908086</t>
+          <t>948852</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>893804</t>
+          <t>936239</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>918055</t>
+          <t>959742</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22865</t>
+          <t>23814</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14226</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34316</t>
+          <t>37169</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21965</t>
+          <t>22936</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14675</t>
+          <t>15797</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30815</t>
+          <t>32132</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>44830</t>
+          <t>46749</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33902</t>
+          <t>35280</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60659</t>
+          <t>60077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>513473</t>
+          <t>597023</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>502022</t>
+          <t>583668</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>522112</t>
+          <t>605587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>570037</t>
+          <t>600257</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>561187</t>
+          <t>591061</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>577327</t>
+          <t>607396</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1083510</t>
+          <t>1197280</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1067681</t>
+          <t>1183952</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1094438</t>
+          <t>1208749</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31938</t>
+          <t>34440</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49269</t>
+          <t>48255</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35853</t>
+          <t>36732</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27845</t>
+          <t>27115</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46829</t>
+          <t>45180</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>67791</t>
+          <t>71172</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42927</t>
+          <t>57526</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89000</t>
+          <t>88481</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>855848</t>
+          <t>666177</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>838517</t>
+          <t>652362</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>875061</t>
+          <t>676525</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>677028</t>
+          <t>700154</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>666052</t>
+          <t>691706</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>685036</t>
+          <t>709771</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1532876</t>
+          <t>1366332</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1511667</t>
+          <t>1349023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1557740</t>
+          <t>1379978</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>17397</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>10481</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25892</t>
+          <t>26715</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19887</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13936</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27336</t>
+          <t>30522</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>36488</t>
+          <t>39646</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27724</t>
+          <t>29705</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48135</t>
+          <t>51405</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>544633</t>
+          <t>591949</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>535342</t>
+          <t>582631</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>550981</t>
+          <t>598865</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>528018</t>
+          <t>586606</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>520569</t>
+          <t>578333</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>533969</t>
+          <t>593196</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1072651</t>
+          <t>1178556</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1061004</t>
+          <t>1166797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1081415</t>
+          <t>1188497</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -11425,12 +11425,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9072</t>
+          <t>9535</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -11493,17 +11493,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>364892</t>
+          <t>403456</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>360718</t>
+          <t>398942</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>366928</t>
+          <t>405863</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,27 +11528,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>607199</t>
+          <t>437944</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>603971</t>
+          <t>434896</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>972091</t>
+          <t>841400</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>967461</t>
+          <t>836711</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>975050</t>
+          <t>844309</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>543</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,22 +11793,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>539</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6699</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -11836,7 +11836,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>423789</t>
+          <t>462233</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>419715</t>
+          <t>457383</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>425354</t>
+          <t>464066</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,27 +11906,27 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>706548</t>
+          <t>772431</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>701891</t>
+          <t>767624</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>708115</t>
+          <t>774268</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>90082</t>
+          <t>94807</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67409</t>
+          <t>77178</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>110563</t>
+          <t>116429</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>110929</t>
+          <t>117402</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>86964</t>
+          <t>100735</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>131265</t>
+          <t>139588</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>201011</t>
+          <t>212209</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>170575</t>
+          <t>187093</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>235060</t>
+          <t>245828</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3369735</t>
+          <t>3437955</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3349254</t>
+          <t>3416333</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3392408</t>
+          <t>3455584</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3601351</t>
+          <t>3619552</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3581015</t>
+          <t>3597366</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3625316</t>
+          <t>3636219</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6971086</t>
+          <t>7057507</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6937037</t>
+          <t>7023888</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7001522</t>
+          <t>7082623</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
